--- a/Master_Data.xlsx
+++ b/Master_Data.xlsx
@@ -8,15 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://comoliferrari-my.sharepoint.com/personal/andrea_pagnini_comoliferrari_it/Documents/Documenti/Cata&amp;InfoTech/TOOL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{99F886DF-463D-41FE-9BA4-3EB527A99612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E9D996F-0CA4-4B07-8137-4940CF4A8D9D}"/>
+  <xr:revisionPtr revIDLastSave="69" documentId="8_{99F886DF-463D-41FE-9BA4-3EB527A99612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF9CE8B2-822F-4DDB-960C-5B24C5872520}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F2E6004E-CD67-4EC6-9F55-D9D6526A83F2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F2E6004E-CD67-4EC6-9F55-D9D6526A83F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Ambiti" sheetId="1" r:id="rId1"/>
     <sheet name="Mapping" sheetId="2" r:id="rId2"/>
     <sheet name="Blacklist" sheetId="3" r:id="rId3"/>
+    <sheet name="Legenda" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Mapping!$D$1:$D$11</definedName>
+    <definedName name="Corrente">Legenda!$C$2:$C$19</definedName>
+    <definedName name="Curve">Legenda!$D$2:$D$7</definedName>
+    <definedName name="Pdi">Legenda!$B$2:$B$10</definedName>
+    <definedName name="Poli">Legenda!$A$2:$A$7</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="72">
   <si>
     <t>Brand</t>
   </si>
@@ -158,6 +166,105 @@
   </si>
   <si>
     <t>Z</t>
+  </si>
+  <si>
+    <t>4.5kA</t>
+  </si>
+  <si>
+    <t>0.5A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>6kA</t>
+  </si>
+  <si>
+    <t>1A</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>10kA</t>
+  </si>
+  <si>
+    <t>2A</t>
+  </si>
+  <si>
+    <t>3P</t>
+  </si>
+  <si>
+    <t>3A</t>
+  </si>
+  <si>
+    <t>3P+N</t>
+  </si>
+  <si>
+    <t>4A</t>
+  </si>
+  <si>
+    <t>4P</t>
+  </si>
+  <si>
+    <t>6A</t>
+  </si>
+  <si>
+    <t>MA (Solo Magnetico)</t>
+  </si>
+  <si>
+    <t>50kA</t>
+  </si>
+  <si>
+    <t>13A</t>
+  </si>
+  <si>
+    <t>70kA</t>
+  </si>
+  <si>
+    <t>20A</t>
+  </si>
+  <si>
+    <t>25A</t>
+  </si>
+  <si>
+    <t>32A</t>
+  </si>
+  <si>
+    <t>40A</t>
+  </si>
+  <si>
+    <t>50A</t>
+  </si>
+  <si>
+    <t>63A</t>
+  </si>
+  <si>
+    <t>80A</t>
+  </si>
+  <si>
+    <t>100A</t>
+  </si>
+  <si>
+    <t>125A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrente </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curve </t>
+  </si>
+  <si>
+    <t>Pdi</t>
+  </si>
+  <si>
+    <t>Curve</t>
+  </si>
+  <si>
+    <t>1P+N (2 mod)</t>
+  </si>
+  <si>
+    <t>1P+N (1 mod)</t>
   </si>
 </sst>
 </file>
@@ -215,7 +322,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -223,34 +330,73 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -268,6 +414,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -590,10 +740,9 @@
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -608,46 +757,46 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="A3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="A5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>10</v>
       </c>
     </row>
@@ -658,273 +807,674 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F1F79D7-FB12-4E25-8507-7AA13858FB1A}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.21875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="10" style="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.21875" style="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.77734375" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="13"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="7" t="s">
+      <c r="A2" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="6">
         <v>1</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="7" t="s">
+      <c r="A3" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="6">
         <v>1</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="6">
         <v>2</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="A4" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="7">
+      <c r="E4" s="6">
         <v>4</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="6">
         <v>2</v>
       </c>
-      <c r="G4" s="8" t="s">
+      <c r="G4" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="7" t="s">
+      <c r="A5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>210</v>
       </c>
-      <c r="F5" s="7">
-        <v>3</v>
-      </c>
-      <c r="G5" s="8" t="s">
+      <c r="F5" s="6">
+        <v>3</v>
+      </c>
+      <c r="G5" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="7" t="s">
+      <c r="A6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6">
         <v>216</v>
       </c>
-      <c r="F6" s="7">
-        <v>3</v>
-      </c>
-      <c r="G6" s="8" t="s">
+      <c r="F6" s="6">
+        <v>3</v>
+      </c>
+      <c r="G6" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="7" t="s">
+      <c r="A7" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <v>1</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="7" t="s">
+      <c r="A8" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="6">
         <v>6</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <v>2</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="7" t="s">
+      <c r="A9" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="6">
         <v>2</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="6">
         <v>2</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="G9" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="7" t="s">
+      <c r="A10" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="6">
         <v>10</v>
       </c>
-      <c r="F10" s="7">
-        <v>3</v>
-      </c>
-      <c r="G10" s="8" t="s">
+      <c r="F10" s="6">
+        <v>3</v>
+      </c>
+      <c r="G10" s="14" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="7" t="s">
+      <c r="A11" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="6">
         <v>16</v>
       </c>
-      <c r="F11" s="7">
-        <v>3</v>
-      </c>
-      <c r="G11" s="8" t="s">
+      <c r="F11" s="6">
+        <v>3</v>
+      </c>
+      <c r="G11" s="14" t="s">
         <v>20</v>
       </c>
     </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C12" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C14" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="C15" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="17" spans="1:6" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F18" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19" s="16">
+        <v>1</v>
+      </c>
+      <c r="F19" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="16">
+        <v>2</v>
+      </c>
+      <c r="F20" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="16">
+        <v>3</v>
+      </c>
+      <c r="F21" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="16">
+        <v>4</v>
+      </c>
+      <c r="F22" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="E23" s="15">
+        <v>5</v>
+      </c>
+      <c r="F23" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E24" s="16">
+        <v>6</v>
+      </c>
+      <c r="F24" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="16">
+        <v>4</v>
+      </c>
+      <c r="F25" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="16">
+        <v>7</v>
+      </c>
+      <c r="F26" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" s="16">
+        <v>6</v>
+      </c>
+      <c r="F27" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E28" s="16">
+        <v>7</v>
+      </c>
+      <c r="F28" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" s="16">
+        <v>8</v>
+      </c>
+      <c r="F29" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E30" s="16">
+        <v>6</v>
+      </c>
+      <c r="F30" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A31" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E31" s="16">
+        <v>10</v>
+      </c>
+      <c r="F31" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A32" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="16">
+        <v>16</v>
+      </c>
+      <c r="F32" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A34" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E34" s="16">
+        <v>0</v>
+      </c>
+      <c r="F34" s="8">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1 D305:D1048576" xr:uid="{39E08784-0378-436C-94BF-78038947CDD5}">
+      <formula1>INDIRECT($C2)</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D39:D304 D2:D38" xr:uid="{E71B78E2-F093-4D08-BE91-FE41798107EC}">
+      <formula1>INDIRECT($C2)</formula1>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" display="https://www.google.com/search?q=https://www.se.com/it/it/product/" xr:uid="{92B18104-5B97-40D3-B2AA-E8045AD7CF98}"/>
     <hyperlink ref="G3" r:id="rId2" display="https://www.google.com/search?q=https://www.se.com/it/it/product/" xr:uid="{23DE5078-916B-4227-9AF2-2ED91058A000}"/>
@@ -946,11 +1496,10 @@
   <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.21875" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="22" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="16384" width="8.88671875" style="3"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -968,102 +1517,322 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="A3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="A5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="s">
+      <c r="A7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="4" t="s">
+      <c r="A8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>38</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B75BA495-577F-4ED7-BECC-5383B32EF7AE}">
+  <dimension ref="A1:D19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.6640625" customWidth="1"/>
+    <col min="2" max="2" width="30.88671875" customWidth="1"/>
+    <col min="3" max="3" width="28" customWidth="1"/>
+    <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="12"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="12"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" s="12"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="12"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="12"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="12"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="D14" s="12"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" s="12"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="D16" s="12"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="12"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="D18" s="12"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="D19" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Master_Data.xlsx
+++ b/Master_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://comoliferrari-my.sharepoint.com/personal/andrea_pagnini_comoliferrari_it/Documents/Documenti/Cata&amp;InfoTech/TOOL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="69" documentId="8_{99F886DF-463D-41FE-9BA4-3EB527A99612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF9CE8B2-822F-4DDB-960C-5B24C5872520}"/>
+  <xr:revisionPtr revIDLastSave="93" documentId="8_{99F886DF-463D-41FE-9BA4-3EB527A99612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC3E9961-AAF0-40B8-A1DF-3907893FADB2}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F2E6004E-CD67-4EC6-9F55-D9D6526A83F2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{F2E6004E-CD67-4EC6-9F55-D9D6526A83F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Ambiti" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <definedName name="Corrente">Legenda!$C$2:$C$19</definedName>
     <definedName name="Curve">Legenda!$D$2:$D$7</definedName>
     <definedName name="Pdi">Legenda!$B$2:$B$10</definedName>
-    <definedName name="Poli">Legenda!$A$2:$A$7</definedName>
+    <definedName name="Poli">Legenda!$A$2:$A$9</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="76">
   <si>
     <t>Brand</t>
   </si>
@@ -258,20 +258,32 @@
     <t>Pdi</t>
   </si>
   <si>
-    <t>Curve</t>
-  </si>
-  <si>
     <t>1P+N (2 mod)</t>
   </si>
   <si>
     <t>1P+N (1 mod)</t>
+  </si>
+  <si>
+    <t>Potenza / Alta Corrente</t>
+  </si>
+  <si>
+    <t>5SP</t>
+  </si>
+  <si>
+    <t>Residenziale/Terziario</t>
+  </si>
+  <si>
+    <t>Alto PDI</t>
+  </si>
+  <si>
+    <t>A</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -299,13 +311,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
@@ -322,7 +327,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -330,27 +335,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
@@ -364,39 +354,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -737,11 +710,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E139F73-8D5B-447B-B9DD-DEC91FC91559}">
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -783,7 +756,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>9</v>
@@ -798,6 +771,17 @@
       </c>
       <c r="C5" s="4" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -807,39 +791,39 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F1F79D7-FB12-4E25-8507-7AA13858FB1A}">
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.21875" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.77734375" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="13"/>
+    <col min="1" max="1" width="10" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.44140625" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.21875" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5546875" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.77734375" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.88671875" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="6" t="s">
         <v>16</v>
       </c>
     </row>
@@ -862,7 +846,7 @@
       <c r="F2" s="6">
         <v>1</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -885,7 +869,7 @@
       <c r="F3" s="6">
         <v>2</v>
       </c>
-      <c r="G3" s="14" t="s">
+      <c r="G3" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -908,7 +892,7 @@
       <c r="F4" s="6">
         <v>2</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -931,7 +915,7 @@
       <c r="F5" s="6">
         <v>3</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -954,7 +938,7 @@
       <c r="F6" s="6">
         <v>3</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -977,7 +961,7 @@
       <c r="F7" s="6">
         <v>1</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1000,7 +984,7 @@
       <c r="F8" s="6">
         <v>2</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1023,7 +1007,7 @@
       <c r="F9" s="6">
         <v>2</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1046,7 +1030,7 @@
       <c r="F10" s="6">
         <v>3</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="9" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1069,409 +1053,659 @@
       <c r="F11" s="6">
         <v>3</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C12" s="6" t="s">
+      <c r="A12" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F14" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="10">
+        <v>1</v>
+      </c>
+      <c r="F15" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="10">
+        <v>2</v>
+      </c>
+      <c r="F16" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="10">
+        <v>3</v>
+      </c>
+      <c r="F17" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="10">
+        <v>4</v>
+      </c>
+      <c r="F18" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="10">
+        <v>5</v>
+      </c>
+      <c r="F19" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E20" s="10">
+        <v>0</v>
+      </c>
+      <c r="F20" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="10">
+        <v>2</v>
+      </c>
+      <c r="F21" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="10">
+        <v>3</v>
+      </c>
+      <c r="F22" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="10">
+        <v>4</v>
+      </c>
+      <c r="F23" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="6" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C13" s="6" t="s">
+      <c r="D24" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="10">
+        <v>3</v>
+      </c>
+      <c r="F24" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E25" s="10">
+        <v>6</v>
+      </c>
+      <c r="F25" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="10">
+        <v>4</v>
+      </c>
+      <c r="F26" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" s="10">
+        <v>7</v>
+      </c>
+      <c r="F27" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D28" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E28" s="10">
+        <v>8</v>
+      </c>
+      <c r="F28" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="10">
+        <v>4</v>
+      </c>
+      <c r="F29" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E30" s="10">
+        <v>5</v>
+      </c>
+      <c r="F30" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" s="10">
+        <v>6</v>
+      </c>
+      <c r="F31" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E32" s="10">
+        <v>7</v>
+      </c>
+      <c r="F32" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" s="10">
+        <v>8</v>
+      </c>
+      <c r="F33" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D34" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="10">
+        <v>6</v>
+      </c>
+      <c r="F34" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D35" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E35" s="10">
+        <v>7</v>
+      </c>
+      <c r="F35" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E36" s="10">
+        <v>8</v>
+      </c>
+      <c r="F36" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C37" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D37" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E37" s="10">
+        <v>6</v>
+      </c>
+      <c r="F37" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="10">
+        <v>10</v>
+      </c>
+      <c r="F38" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" s="10" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C14" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C15" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="1:6" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C18" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D18" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" s="16">
-        <v>1</v>
-      </c>
-      <c r="F19" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E20" s="16">
-        <v>2</v>
-      </c>
-      <c r="F20" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" s="16">
-        <v>3</v>
-      </c>
-      <c r="F21" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="E22" s="16">
-        <v>4</v>
-      </c>
-      <c r="F22" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>70</v>
-      </c>
-      <c r="E23" s="15">
-        <v>5</v>
-      </c>
-      <c r="F23" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="E24" s="16">
-        <v>6</v>
-      </c>
-      <c r="F24" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E25" s="16">
-        <v>4</v>
-      </c>
-      <c r="F25" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="D26" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" s="16">
-        <v>7</v>
-      </c>
-      <c r="F26" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="E27" s="16">
-        <v>6</v>
-      </c>
-      <c r="F27" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="E28" s="16">
-        <v>7</v>
-      </c>
-      <c r="F28" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="D29" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="E29" s="16">
-        <v>8</v>
-      </c>
-      <c r="F29" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="16" t="s">
+      <c r="E39" s="10">
+        <v>16</v>
+      </c>
+      <c r="F39" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D30" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="E30" s="16">
-        <v>6</v>
-      </c>
-      <c r="F30" s="8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="16" t="s">
+      <c r="D40" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E40" s="10">
+        <v>63</v>
+      </c>
+      <c r="F40" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C41" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D31" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E31" s="16">
-        <v>10</v>
-      </c>
-      <c r="F31" s="8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="16" t="s">
+      <c r="D41" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E41" s="10">
+        <v>80</v>
+      </c>
+      <c r="F41" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C42" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D32" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E32" s="16">
-        <v>16</v>
-      </c>
-      <c r="F32" s="8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="D33" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E34" s="16">
-        <v>0</v>
-      </c>
-      <c r="F34" s="8">
-        <v>2</v>
-      </c>
+      <c r="D42" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="E42" s="10">
+        <v>91</v>
+      </c>
+      <c r="F42" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E43" s="10">
+        <v>92</v>
+      </c>
+      <c r="F43" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C44" s="11"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1 D305:D1048576" xr:uid="{39E08784-0378-436C-94BF-78038947CDD5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1 D299:D1048576" xr:uid="{39E08784-0378-436C-94BF-78038947CDD5}">
       <formula1>INDIRECT($C2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D39:D304 D2:D38" xr:uid="{E71B78E2-F093-4D08-BE91-FE41798107EC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D138:D298 D2:D137" xr:uid="{E71B78E2-F093-4D08-BE91-FE41798107EC}">
       <formula1>INDIRECT($C2)</formula1>
     </dataValidation>
   </dataValidations>
@@ -1631,208 +1865,208 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="2" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="4" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="4" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="4" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="D7" s="4" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>69</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D8" s="12"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="12"/>
+      <c r="D9" s="4"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11" t="s">
+      <c r="A10" s="3"/>
+      <c r="B10" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="12"/>
+      <c r="D10" s="4"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11" t="s">
+      <c r="A11" s="3"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="12"/>
+      <c r="D11" s="4"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11" t="s">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D12" s="12"/>
+      <c r="D12" s="4"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11" t="s">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D13" s="12"/>
+      <c r="D13" s="4"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11" t="s">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D14" s="12"/>
+      <c r="D14" s="4"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11"/>
-      <c r="C15" s="11" t="s">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="12"/>
+      <c r="D15" s="4"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11" t="s">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D16" s="12"/>
+      <c r="D16" s="4"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="11" t="s">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="12"/>
+      <c r="D17" s="4"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11" t="s">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="12"/>
+      <c r="D18" s="4"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11" t="s">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="12"/>
+      <c r="D19" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Master_Data.xlsx
+++ b/Master_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://comoliferrari-my.sharepoint.com/personal/andrea_pagnini_comoliferrari_it/Documents/Documenti/Cata&amp;InfoTech/TOOL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="93" documentId="8_{99F886DF-463D-41FE-9BA4-3EB527A99612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC3E9961-AAF0-40B8-A1DF-3907893FADB2}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="8_{99F886DF-463D-41FE-9BA4-3EB527A99612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7E13A6A-C889-4A33-B575-3DE576F47F55}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{F2E6004E-CD67-4EC6-9F55-D9D6526A83F2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F2E6004E-CD67-4EC6-9F55-D9D6526A83F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Ambiti" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Legenda" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Mapping!$D$1:$D$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Mapping!$A$1:$G$53</definedName>
     <definedName name="Corrente">Legenda!$C$2:$C$19</definedName>
     <definedName name="Curve">Legenda!$D$2:$D$7</definedName>
     <definedName name="Pdi">Legenda!$B$2:$B$10</definedName>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="75">
   <si>
     <t>Brand</t>
   </si>
@@ -271,9 +271,6 @@
   </si>
   <si>
     <t>Residenziale/Terziario</t>
-  </si>
-  <si>
-    <t>Alto PDI</t>
   </si>
   <si>
     <t>A</t>
@@ -340,7 +337,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
@@ -354,22 +351,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -387,10 +379,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -773,14 +761,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="5" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="10" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="4" t="s">
         <v>72</v>
       </c>
     </row>
@@ -791,921 +779,1118 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F1F79D7-FB12-4E25-8507-7AA13858FB1A}">
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10" style="8" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.44140625" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5546875" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.77734375" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="8"/>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="6" t="s">
+      <c r="A2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="5">
         <v>1</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="G2" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="6" t="s">
+      <c r="A3" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="5">
         <v>1</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="5">
         <v>2</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="G3" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
+      <c r="A4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="5">
         <v>4</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="5">
         <v>2</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="6" t="s">
+      <c r="A5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="5">
         <v>210</v>
       </c>
-      <c r="F5" s="6">
-        <v>3</v>
-      </c>
-      <c r="G5" s="9" t="s">
+      <c r="F5" s="5">
+        <v>3</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="6" t="s">
+      <c r="A6" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <v>216</v>
       </c>
-      <c r="F6" s="6">
-        <v>3</v>
-      </c>
-      <c r="G6" s="9" t="s">
+      <c r="F6" s="5">
+        <v>3</v>
+      </c>
+      <c r="G6" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="6" t="s">
+      <c r="A7" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="5">
         <v>1</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="6" t="s">
+      <c r="A8" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="5">
         <v>6</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="5">
         <v>2</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="6" t="s">
+      <c r="A9" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="5">
         <v>2</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="5">
         <v>2</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B10" s="6" t="s">
+      <c r="A10" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="5">
         <v>10</v>
       </c>
-      <c r="F10" s="6">
-        <v>3</v>
-      </c>
-      <c r="G10" s="9" t="s">
+      <c r="F10" s="5">
+        <v>3</v>
+      </c>
+      <c r="G10" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" s="6" t="s">
+      <c r="A11" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="5">
         <v>16</v>
       </c>
-      <c r="F11" s="6">
-        <v>3</v>
-      </c>
-      <c r="G11" s="9" t="s">
+      <c r="F11" s="5">
+        <v>3</v>
+      </c>
+      <c r="G11" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="10" t="s">
+      <c r="A12" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C13" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D13" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E13" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F13" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="10" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C14" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E14" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F14" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="10" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C15" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D15" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E15" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F15" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="10" t="s">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C16" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D16" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="10">
+      <c r="E16" s="7">
         <v>1</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F16" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="10" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C17" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D17" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="10">
+      <c r="E17" s="7">
         <v>2</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F17" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="10" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C18" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D18" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="10">
-        <v>3</v>
-      </c>
-      <c r="F17" s="7">
+      <c r="E18" s="7">
+        <v>3</v>
+      </c>
+      <c r="F18" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="10" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C19" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D19" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E18" s="10">
+      <c r="E19" s="7">
         <v>4</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F19" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="10" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="10" t="s">
+      <c r="C20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D20" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E20" s="7">
         <v>5</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F20" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="10" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C21" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D21" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" s="7">
+        <v>1</v>
+      </c>
+      <c r="F21" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="7">
+        <v>2</v>
+      </c>
+      <c r="F22" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="7">
+        <v>3</v>
+      </c>
+      <c r="F23" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="7">
+        <v>4</v>
+      </c>
+      <c r="F24" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E25" s="7">
         <v>0</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F25" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="10" t="s">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="10" t="s">
+      <c r="C26" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D26" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="10">
+      <c r="E26" s="7">
         <v>2</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F26" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="10" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C22" s="10" t="s">
+      <c r="C27" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D27" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E22" s="10">
-        <v>3</v>
-      </c>
-      <c r="F22" s="7">
+      <c r="E27" s="7">
+        <v>3</v>
+      </c>
+      <c r="F27" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="10" t="s">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="C28" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D28" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E28" s="7">
         <v>4</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F28" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="10" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C29" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D29" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E24" s="10">
-        <v>3</v>
-      </c>
-      <c r="F24" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="10" t="s">
+      <c r="E29" s="7">
+        <v>3</v>
+      </c>
+      <c r="F29" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C30" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D30" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E30" s="7">
         <v>6</v>
       </c>
-      <c r="F25" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="10" t="s">
+      <c r="F30" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C31" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D31" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E26" s="10">
+      <c r="E31" s="7">
         <v>4</v>
       </c>
-      <c r="F26" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="10" t="s">
+      <c r="F31" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C32" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D32" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E32" s="7">
         <v>7</v>
       </c>
-      <c r="F27" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" s="10" t="s">
+      <c r="F32" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E33" s="7">
+        <v>3</v>
+      </c>
+      <c r="F33" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E34" s="7">
+        <v>6</v>
+      </c>
+      <c r="F34" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" s="7">
+        <v>4</v>
+      </c>
+      <c r="F35" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="7">
+        <v>4</v>
+      </c>
+      <c r="F36" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D28" s="10" t="s">
+      <c r="C37" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E28" s="10">
-        <v>8</v>
-      </c>
-      <c r="F28" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" s="10" t="s">
+      <c r="E37" s="7">
+        <v>5</v>
+      </c>
+      <c r="F37" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E38" s="7">
+        <v>6</v>
+      </c>
+      <c r="F38" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E39" s="7">
+        <v>7</v>
+      </c>
+      <c r="F39" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E40" s="7">
+        <v>8</v>
+      </c>
+      <c r="F40" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E41" s="7">
+        <v>6</v>
+      </c>
+      <c r="F41" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E42" s="7">
+        <v>7</v>
+      </c>
+      <c r="F42" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="E29" s="10">
+      <c r="C43" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E43" s="7">
+        <v>6</v>
+      </c>
+      <c r="F43" s="8">
         <v>4</v>
       </c>
-      <c r="F29" s="7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" s="10" t="s">
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E44" s="7">
+        <v>7</v>
+      </c>
+      <c r="F44" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E45" s="7">
+        <v>8</v>
+      </c>
+      <c r="F45" s="8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C30" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="E30" s="10">
+      <c r="C46" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="E46" s="7">
+        <v>6</v>
+      </c>
+      <c r="F46" s="8">
         <v>5</v>
       </c>
-      <c r="F30" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" s="10" t="s">
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C31" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E31" s="10">
-        <v>6</v>
-      </c>
-      <c r="F31" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B32" s="10" t="s">
+      <c r="C47" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E47" s="7">
         <v>10</v>
       </c>
-      <c r="C32" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E32" s="10">
-        <v>7</v>
-      </c>
-      <c r="F32" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" s="10" t="s">
+      <c r="F47" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C33" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E33" s="10">
-        <v>8</v>
-      </c>
-      <c r="F33" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" s="10" t="s">
+      <c r="C48" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E48" s="7">
+        <v>16</v>
+      </c>
+      <c r="F48" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E49" s="7">
+        <v>10</v>
+      </c>
+      <c r="F49" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E50" s="7">
+        <v>16</v>
+      </c>
+      <c r="F50" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C34" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="E34" s="10">
-        <v>6</v>
-      </c>
-      <c r="F34" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B35" s="10" t="s">
+      <c r="C51" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E51" s="7">
+        <v>80</v>
+      </c>
+      <c r="F51" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B52" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C35" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E35" s="10">
-        <v>7</v>
-      </c>
-      <c r="F35" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B36" s="10" t="s">
+      <c r="C52" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="E52" s="7">
+        <v>91</v>
+      </c>
+      <c r="F52" s="8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B53" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C36" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="E36" s="10">
-        <v>8</v>
-      </c>
-      <c r="F36" s="7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="10" t="s">
+      <c r="C53" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D37" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="E37" s="10">
-        <v>6</v>
-      </c>
-      <c r="F37" s="7">
+      <c r="D53" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E53" s="7">
+        <v>92</v>
+      </c>
+      <c r="F53" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E38" s="10">
-        <v>10</v>
-      </c>
-      <c r="F38" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E39" s="10">
-        <v>16</v>
-      </c>
-      <c r="F39" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="E40" s="10">
-        <v>63</v>
-      </c>
-      <c r="F40" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="E41" s="10">
-        <v>80</v>
-      </c>
-      <c r="F41" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E42" s="10">
-        <v>91</v>
-      </c>
-      <c r="F42" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="E43" s="10">
-        <v>92</v>
-      </c>
-      <c r="F43" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C44" s="11"/>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:G53" xr:uid="{9F1F79D7-FB12-4E25-8507-7AA13858FB1A}"/>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1 D299:D1048576" xr:uid="{39E08784-0378-436C-94BF-78038947CDD5}">
       <formula1>INDIRECT($C2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D138:D298 D2:D137" xr:uid="{E71B78E2-F093-4D08-BE91-FE41798107EC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D138:D298 D2:D11 D54:D137" xr:uid="{E71B78E2-F093-4D08-BE91-FE41798107EC}">
       <formula1>INDIRECT($C2)</formula1>
     </dataValidation>
   </dataValidations>
@@ -1722,6 +1907,7 @@
     <hyperlink ref="G11" r:id="rId10" display="https://www.google.com/search?q=https://www.se.com/it/it/product/" xr:uid="{0F0B6765-674C-46E0-9782-391EDED3726B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId11"/>
 </worksheet>
 </file>
 

--- a/Master_Data.xlsx
+++ b/Master_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://comoliferrari-my.sharepoint.com/personal/andrea_pagnini_comoliferrari_it/Documents/Documenti/Cata&amp;InfoTech/TOOL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="8_{99F886DF-463D-41FE-9BA4-3EB527A99612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7E13A6A-C889-4A33-B575-3DE576F47F55}"/>
+  <xr:revisionPtr revIDLastSave="130" documentId="8_{99F886DF-463D-41FE-9BA4-3EB527A99612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{722B9165-D847-4131-8E72-BD768C23C39D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F2E6004E-CD67-4EC6-9F55-D9D6526A83F2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{F2E6004E-CD67-4EC6-9F55-D9D6526A83F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Ambiti" sheetId="1" r:id="rId1"/>
@@ -19,9 +19,9 @@
     <sheet name="Legenda" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Mapping!$A$1:$G$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Mapping!$A$1:$G$52</definedName>
     <definedName name="Corrente">Legenda!$C$2:$C$19</definedName>
-    <definedName name="Curve">Legenda!$D$2:$D$7</definedName>
+    <definedName name="Curva">Legenda!$D$2:$D$7</definedName>
     <definedName name="Pdi">Legenda!$B$2:$B$10</definedName>
     <definedName name="Poli">Legenda!$A$2:$A$9</definedName>
   </definedNames>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="72">
   <si>
     <t>Brand</t>
   </si>
@@ -141,9 +141,6 @@
     <t>Valore_da_Escludere</t>
   </si>
   <si>
-    <t>Potere_Interruzione</t>
-  </si>
-  <si>
     <t>15kA</t>
   </si>
   <si>
@@ -247,12 +244,6 @@
   </si>
   <si>
     <t>125A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Corrente </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curve </t>
   </si>
   <si>
     <t>Pdi</t>
@@ -337,7 +328,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
@@ -356,12 +347,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -744,7 +729,7 @@
         <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>9</v>
@@ -766,10 +751,10 @@
         <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -779,7 +764,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F1F79D7-FB12-4E25-8507-7AA13858FB1A}">
-  <dimension ref="A1:G53"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -1045,852 +1030,832 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F14" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1</v>
+      </c>
+      <c r="F15" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="3">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E17" s="3">
+        <v>3</v>
+      </c>
+      <c r="F17" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" s="3">
+        <v>4</v>
+      </c>
+      <c r="F18" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19" s="3">
+        <v>5</v>
+      </c>
+      <c r="F19" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="3">
+        <v>1</v>
+      </c>
+      <c r="F20" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="3">
+        <v>2</v>
+      </c>
+      <c r="F21" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E22" s="3">
+        <v>3</v>
+      </c>
+      <c r="F22" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="3">
+        <v>4</v>
+      </c>
+      <c r="F23" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E24" s="3">
         <v>0</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B13" s="7" t="s">
+      <c r="F24" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" s="3">
+        <v>2</v>
+      </c>
+      <c r="F25" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="E26" s="3">
+        <v>3</v>
+      </c>
+      <c r="F26" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E27" s="3">
+        <v>4</v>
+      </c>
+      <c r="F27" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="7" t="s">
+      <c r="C28" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" s="3">
+        <v>3</v>
+      </c>
+      <c r="F28" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B14" s="7" t="s">
+      <c r="C29" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" s="3">
+        <v>6</v>
+      </c>
+      <c r="F29" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E30" s="3">
+        <v>4</v>
+      </c>
+      <c r="F30" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="3">
+        <v>7</v>
+      </c>
+      <c r="F31" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="7" t="s">
+      <c r="C32" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E32" s="3">
+        <v>3</v>
+      </c>
+      <c r="F32" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="F15" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="7" t="s">
+      <c r="C33" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" s="3">
+        <v>6</v>
+      </c>
+      <c r="F33" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E34" s="3">
+        <v>4</v>
+      </c>
+      <c r="F34" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E35" s="3">
+        <v>4</v>
+      </c>
+      <c r="F35" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1</v>
-      </c>
-      <c r="F16" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="7" t="s">
+      <c r="C36" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E36" s="3">
+        <v>5</v>
+      </c>
+      <c r="F36" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E17" s="7">
-        <v>2</v>
-      </c>
-      <c r="F17" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B18" s="7" t="s">
+      <c r="C37" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E37" s="3">
+        <v>6</v>
+      </c>
+      <c r="F37" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E18" s="7">
-        <v>3</v>
-      </c>
-      <c r="F18" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B19" s="7" t="s">
+      <c r="C38" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E38" s="3">
+        <v>7</v>
+      </c>
+      <c r="F38" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D19" s="7" t="s">
+      <c r="C39" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E39" s="3">
+        <v>8</v>
+      </c>
+      <c r="F39" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E40" s="3">
+        <v>6</v>
+      </c>
+      <c r="F40" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E41" s="3">
+        <v>7</v>
+      </c>
+      <c r="F41" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="E42" s="3">
+        <v>6</v>
+      </c>
+      <c r="F42" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E43" s="3">
+        <v>7</v>
+      </c>
+      <c r="F43" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E44" s="3">
+        <v>8</v>
+      </c>
+      <c r="F44" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="7">
-        <v>4</v>
-      </c>
-      <c r="F19" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="7" t="s">
+      <c r="E45" s="3">
+        <v>6</v>
+      </c>
+      <c r="F45" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D20" s="7" t="s">
+      <c r="C46" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E46" s="3">
+        <v>10</v>
+      </c>
+      <c r="F46" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E47" s="3">
+        <v>16</v>
+      </c>
+      <c r="F47" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E48" s="3">
+        <v>10</v>
+      </c>
+      <c r="F48" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E49" s="3">
+        <v>16</v>
+      </c>
+      <c r="F49" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E20" s="7">
+      <c r="C50" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E50" s="3">
+        <v>80</v>
+      </c>
+      <c r="F50" s="4">
         <v>5</v>
       </c>
-      <c r="F20" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="7">
-        <v>1</v>
-      </c>
-      <c r="F21" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22" s="7">
-        <v>2</v>
-      </c>
-      <c r="F22" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E23" s="7">
-        <v>3</v>
-      </c>
-      <c r="F23" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E24" s="7">
-        <v>4</v>
-      </c>
-      <c r="F24" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0</v>
-      </c>
-      <c r="F25" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26" s="7">
-        <v>2</v>
-      </c>
-      <c r="F26" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="E27" s="7">
-        <v>3</v>
-      </c>
-      <c r="F27" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="E28" s="7">
-        <v>4</v>
-      </c>
-      <c r="F28" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E29" s="7">
-        <v>3</v>
-      </c>
-      <c r="F29" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E30" s="7">
-        <v>6</v>
-      </c>
-      <c r="F30" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E31" s="7">
-        <v>4</v>
-      </c>
-      <c r="F31" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E32" s="7">
-        <v>7</v>
-      </c>
-      <c r="F32" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E33" s="7">
-        <v>3</v>
-      </c>
-      <c r="F33" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E34" s="7">
-        <v>6</v>
-      </c>
-      <c r="F34" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E35" s="7">
-        <v>4</v>
-      </c>
-      <c r="F35" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="E36" s="7">
-        <v>4</v>
-      </c>
-      <c r="F36" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E37" s="7">
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E51" s="3">
+        <v>91</v>
+      </c>
+      <c r="F51" s="4">
         <v>5</v>
       </c>
-      <c r="F37" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E38" s="7">
-        <v>6</v>
-      </c>
-      <c r="F38" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E39" s="7">
-        <v>7</v>
-      </c>
-      <c r="F39" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E40" s="7">
-        <v>8</v>
-      </c>
-      <c r="F40" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E41" s="7">
-        <v>6</v>
-      </c>
-      <c r="F41" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E42" s="7">
-        <v>7</v>
-      </c>
-      <c r="F42" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="E43" s="7">
-        <v>6</v>
-      </c>
-      <c r="F43" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="E44" s="7">
-        <v>7</v>
-      </c>
-      <c r="F44" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E45" s="7">
-        <v>8</v>
-      </c>
-      <c r="F45" s="8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B46" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C46" s="7" t="s">
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="C52" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D46" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="E46" s="7">
-        <v>6</v>
-      </c>
-      <c r="F46" s="8">
+      <c r="D52" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E52" s="3">
+        <v>92</v>
+      </c>
+      <c r="F52" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B47" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D47" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E47" s="7">
-        <v>10</v>
-      </c>
-      <c r="F47" s="8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D48" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E48" s="7">
-        <v>16</v>
-      </c>
-      <c r="F48" s="8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="E49" s="7">
-        <v>10</v>
-      </c>
-      <c r="F49" s="8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B50" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C50" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D50" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E50" s="7">
-        <v>16</v>
-      </c>
-      <c r="F50" s="8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B51" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E51" s="7">
-        <v>80</v>
-      </c>
-      <c r="F51" s="8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B52" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D52" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="E52" s="7">
-        <v>91</v>
-      </c>
-      <c r="F52" s="8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D53" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E53" s="7">
-        <v>92</v>
-      </c>
-      <c r="F53" s="8">
-        <v>5</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:G53" xr:uid="{9F1F79D7-FB12-4E25-8507-7AA13858FB1A}"/>
+  <autoFilter ref="A1:G52" xr:uid="{9F1F79D7-FB12-4E25-8507-7AA13858FB1A}"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1 D299:D1048576" xr:uid="{39E08784-0378-436C-94BF-78038947CDD5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1 D298:D1048576" xr:uid="{39E08784-0378-436C-94BF-78038947CDD5}">
       <formula1>INDIRECT($C2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D138:D298 D2:D11 D54:D137" xr:uid="{E71B78E2-F093-4D08-BE91-FE41798107EC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D137:D297 D2:D11 D53:D136" xr:uid="{E71B78E2-F093-4D08-BE91-FE41798107EC}">
       <formula1>INDIRECT($C2)</formula1>
     </dataValidation>
   </dataValidations>
@@ -1944,10 +1909,10 @@
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -1958,10 +1923,10 @@
         <v>5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -1972,10 +1937,10 @@
         <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -1986,10 +1951,10 @@
         <v>5</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -2000,10 +1965,10 @@
         <v>5</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>35</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -2014,10 +1979,10 @@
         <v>5</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -2028,10 +1993,10 @@
         <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2055,13 +2020,13 @@
         <v>21</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -2069,13 +2034,13 @@
         <v>22</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -2083,13 +2048,13 @@
         <v>28</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
@@ -2097,63 +2062,63 @@
         <v>23</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>46</v>
-      </c>
       <c r="D4" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="D5" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>50</v>
-      </c>
       <c r="D6" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>25</v>
@@ -2162,20 +2127,20 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="D9" s="4"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>26</v>
@@ -2186,7 +2151,7 @@
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D11" s="4"/>
     </row>
@@ -2194,7 +2159,7 @@
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D12" s="4"/>
     </row>
@@ -2202,7 +2167,7 @@
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D13" s="4"/>
     </row>
@@ -2210,7 +2175,7 @@
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D14" s="4"/>
     </row>
@@ -2218,7 +2183,7 @@
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D15" s="4"/>
     </row>
@@ -2226,7 +2191,7 @@
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D16" s="4"/>
     </row>
@@ -2234,7 +2199,7 @@
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" s="4"/>
     </row>
@@ -2242,7 +2207,7 @@
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D18" s="4"/>
     </row>
@@ -2250,7 +2215,7 @@
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D19" s="4"/>
     </row>

--- a/Master_Data.xlsx
+++ b/Master_Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://comoliferrari-my.sharepoint.com/personal/andrea_pagnini_comoliferrari_it/Documents/Documenti/Cata&amp;InfoTech/TOOL/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="130" documentId="8_{99F886DF-463D-41FE-9BA4-3EB527A99612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{722B9165-D847-4131-8E72-BD768C23C39D}"/>
+  <xr:revisionPtr revIDLastSave="135" documentId="8_{99F886DF-463D-41FE-9BA4-3EB527A99612}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D6365B4-A23C-49EF-A94F-33244EF72EA1}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{F2E6004E-CD67-4EC6-9F55-D9D6526A83F2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F2E6004E-CD67-4EC6-9F55-D9D6526A83F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Ambiti" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="73">
   <si>
     <t>Brand</t>
   </si>
@@ -265,6 +265,9 @@
   </si>
   <si>
     <t>A</t>
+  </si>
+  <si>
+    <t>https://support.industry.siemens.com/cs/products?search=</t>
   </si>
 </sst>
 </file>
@@ -328,7 +331,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
@@ -348,6 +351,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -364,6 +368,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -773,7 +781,7 @@
     <col min="4" max="4" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.77734375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -1048,6 +1056,9 @@
       <c r="F12" s="4">
         <v>1</v>
       </c>
+      <c r="G12" s="7" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
@@ -1068,6 +1079,9 @@
       <c r="F13" s="4">
         <v>1</v>
       </c>
+      <c r="G13" s="7" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
@@ -1088,6 +1102,9 @@
       <c r="F14" s="4">
         <v>1</v>
       </c>
+      <c r="G14" s="7" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
@@ -1108,6 +1125,9 @@
       <c r="F15" s="4">
         <v>2</v>
       </c>
+      <c r="G15" s="7" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
@@ -1128,8 +1148,11 @@
       <c r="F16" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>8</v>
       </c>
@@ -1148,8 +1171,11 @@
       <c r="F17" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G17" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>8</v>
       </c>
@@ -1168,8 +1194,11 @@
       <c r="F18" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G18" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
         <v>8</v>
       </c>
@@ -1188,8 +1217,11 @@
       <c r="F19" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G19" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
         <v>8</v>
       </c>
@@ -1208,8 +1240,11 @@
       <c r="F20" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G20" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
         <v>8</v>
       </c>
@@ -1228,8 +1263,11 @@
       <c r="F21" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G21" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>8</v>
       </c>
@@ -1248,8 +1286,11 @@
       <c r="F22" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G22" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>8</v>
       </c>
@@ -1268,8 +1309,11 @@
       <c r="F23" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G23" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>8</v>
       </c>
@@ -1288,8 +1332,11 @@
       <c r="F24" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G24" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>8</v>
       </c>
@@ -1308,8 +1355,11 @@
       <c r="F25" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G25" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>8</v>
       </c>
@@ -1328,8 +1378,11 @@
       <c r="F26" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G26" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>8</v>
       </c>
@@ -1348,8 +1401,11 @@
       <c r="F27" s="4">
         <v>2</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G27" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>8</v>
       </c>
@@ -1368,8 +1424,11 @@
       <c r="F28" s="4">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G28" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>8</v>
       </c>
@@ -1388,8 +1447,11 @@
       <c r="F29" s="4">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G29" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>8</v>
       </c>
@@ -1408,8 +1470,11 @@
       <c r="F30" s="4">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G30" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>8</v>
       </c>
@@ -1428,8 +1493,11 @@
       <c r="F31" s="4">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G31" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>8</v>
       </c>
@@ -1448,8 +1516,11 @@
       <c r="F32" s="4">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G32" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>8</v>
       </c>
@@ -1468,8 +1539,11 @@
       <c r="F33" s="4">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G33" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>8</v>
       </c>
@@ -1488,8 +1562,11 @@
       <c r="F34" s="4">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G34" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>8</v>
       </c>
@@ -1508,8 +1585,11 @@
       <c r="F35" s="4">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G35" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>8</v>
       </c>
@@ -1528,8 +1608,11 @@
       <c r="F36" s="4">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G36" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
         <v>8</v>
       </c>
@@ -1548,8 +1631,11 @@
       <c r="F37" s="4">
         <v>4</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G37" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>8</v>
       </c>
@@ -1568,8 +1654,11 @@
       <c r="F38" s="4">
         <v>4</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G38" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>8</v>
       </c>
@@ -1588,8 +1677,11 @@
       <c r="F39" s="4">
         <v>4</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G39" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
         <v>8</v>
       </c>
@@ -1608,8 +1700,11 @@
       <c r="F40" s="4">
         <v>4</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G40" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>8</v>
       </c>
@@ -1628,8 +1723,11 @@
       <c r="F41" s="4">
         <v>4</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G41" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>8</v>
       </c>
@@ -1648,8 +1746,11 @@
       <c r="F42" s="4">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G42" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
         <v>8</v>
       </c>
@@ -1668,8 +1769,11 @@
       <c r="F43" s="4">
         <v>4</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G43" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
         <v>8</v>
       </c>
@@ -1688,8 +1792,11 @@
       <c r="F44" s="4">
         <v>4</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G44" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
         <v>8</v>
       </c>
@@ -1708,8 +1815,11 @@
       <c r="F45" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G45" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
         <v>8</v>
       </c>
@@ -1728,8 +1838,11 @@
       <c r="F46" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G46" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>8</v>
       </c>
@@ -1748,8 +1861,11 @@
       <c r="F47" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G47" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>8</v>
       </c>
@@ -1768,8 +1884,11 @@
       <c r="F48" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G48" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
         <v>8</v>
       </c>
@@ -1788,8 +1907,11 @@
       <c r="F49" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G49" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
         <v>8</v>
       </c>
@@ -1808,8 +1930,11 @@
       <c r="F50" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G50" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>8</v>
       </c>
@@ -1828,8 +1953,11 @@
       <c r="F51" s="4">
         <v>5</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G51" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
         <v>8</v>
       </c>
@@ -1847,6 +1975,9 @@
       </c>
       <c r="F52" s="4">
         <v>5</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1855,7 +1986,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D1 D298:D1048576" xr:uid="{39E08784-0378-436C-94BF-78038947CDD5}">
       <formula1>INDIRECT($C2)</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D137:D297 D2:D11 D53:D136" xr:uid="{E71B78E2-F093-4D08-BE91-FE41798107EC}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D2:D11 D53:D297" xr:uid="{E71B78E2-F093-4D08-BE91-FE41798107EC}">
       <formula1>INDIRECT($C2)</formula1>
     </dataValidation>
   </dataValidations>
@@ -1870,9 +2001,37 @@
     <hyperlink ref="G9" r:id="rId8" display="https://www.google.com/search?q=https://www.se.com/it/it/product/" xr:uid="{6F652B6B-8AC5-4798-BC0C-1DF08564C072}"/>
     <hyperlink ref="G10" r:id="rId9" display="https://www.google.com/search?q=https://www.se.com/it/it/product/" xr:uid="{EC497E26-282A-4607-A811-6CB7E704D608}"/>
     <hyperlink ref="G11" r:id="rId10" display="https://www.google.com/search?q=https://www.se.com/it/it/product/" xr:uid="{0F0B6765-674C-46E0-9782-391EDED3726B}"/>
+    <hyperlink ref="G12" r:id="rId11" xr:uid="{53A255DE-8544-4FCF-A581-27EE579D0FB8}"/>
+    <hyperlink ref="G13:G14" r:id="rId12" display="https://support.industry.siemens.com/cs/products?search=" xr:uid="{6C3D8F21-44F3-40DC-B00A-83A29665E357}"/>
+    <hyperlink ref="G15" r:id="rId13" xr:uid="{1092530B-A9EA-4B20-A24A-DD9BD1C603F2}"/>
+    <hyperlink ref="G18" r:id="rId14" xr:uid="{0A11CFEA-1991-4FBC-A5EC-43D3A5A130E0}"/>
+    <hyperlink ref="G21" r:id="rId15" xr:uid="{CAF9103C-9D2E-4E88-9FCF-9CAC5AC6928F}"/>
+    <hyperlink ref="G24" r:id="rId16" xr:uid="{7FED2D51-9041-4CEC-8C6A-ECB14595B7E8}"/>
+    <hyperlink ref="G27" r:id="rId17" xr:uid="{BC6C29E7-75B4-4560-B6FD-F90AC5204B10}"/>
+    <hyperlink ref="G30" r:id="rId18" xr:uid="{7722D825-88F1-49BF-A69C-0DA17BE44C9E}"/>
+    <hyperlink ref="G33" r:id="rId19" xr:uid="{5997FCAF-9998-4547-80BA-BB0EBB3B71BC}"/>
+    <hyperlink ref="G36" r:id="rId20" xr:uid="{D6ADD2CE-8DDD-4384-B5B0-7D93C2C7FAFC}"/>
+    <hyperlink ref="G39" r:id="rId21" xr:uid="{CC656A03-4476-4EF4-A1EA-5FAB0E5BC7AB}"/>
+    <hyperlink ref="G42" r:id="rId22" xr:uid="{3B8B75BE-33BA-47C2-9346-2B01D62EA974}"/>
+    <hyperlink ref="G45" r:id="rId23" xr:uid="{3303CCBB-0B31-4D07-862C-1FC2DB13061C}"/>
+    <hyperlink ref="G48" r:id="rId24" xr:uid="{C940A33B-CCEB-4BB2-A19E-2F58FFE68B88}"/>
+    <hyperlink ref="G51" r:id="rId25" xr:uid="{5126CBB1-B8E8-417B-B65B-815437EC540B}"/>
+    <hyperlink ref="G16:G17" r:id="rId26" display="https://support.industry.siemens.com/cs/products?search=" xr:uid="{FEA23C29-014F-4B45-82FE-9864E5CB55B1}"/>
+    <hyperlink ref="G19:G20" r:id="rId27" display="https://support.industry.siemens.com/cs/products?search=" xr:uid="{B434013A-4332-4EA1-9A97-B008E8F8131B}"/>
+    <hyperlink ref="G22:G23" r:id="rId28" display="https://support.industry.siemens.com/cs/products?search=" xr:uid="{A5E60447-C2CF-48F4-815C-0EA5BEA8BB5F}"/>
+    <hyperlink ref="G25:G26" r:id="rId29" display="https://support.industry.siemens.com/cs/products?search=" xr:uid="{0ADEC2B7-CE58-47DF-97DC-B103A78B6A0E}"/>
+    <hyperlink ref="G28:G29" r:id="rId30" display="https://support.industry.siemens.com/cs/products?search=" xr:uid="{B18B2415-1D0E-4645-A910-BC2747AFF180}"/>
+    <hyperlink ref="G31:G32" r:id="rId31" display="https://support.industry.siemens.com/cs/products?search=" xr:uid="{1398FE36-8A0A-4FCE-A3A6-8707929DB959}"/>
+    <hyperlink ref="G34:G35" r:id="rId32" display="https://support.industry.siemens.com/cs/products?search=" xr:uid="{329A1FB9-FD02-4182-85C3-F289BA19D1B4}"/>
+    <hyperlink ref="G37:G38" r:id="rId33" display="https://support.industry.siemens.com/cs/products?search=" xr:uid="{1BC0638B-274B-4306-AFFA-4699DF052C5A}"/>
+    <hyperlink ref="G40:G41" r:id="rId34" display="https://support.industry.siemens.com/cs/products?search=" xr:uid="{FFF787FB-E357-44BB-92CA-327725858BBB}"/>
+    <hyperlink ref="G43:G44" r:id="rId35" display="https://support.industry.siemens.com/cs/products?search=" xr:uid="{934F1881-1300-4700-BD66-2672B0BE2394}"/>
+    <hyperlink ref="G46:G47" r:id="rId36" display="https://support.industry.siemens.com/cs/products?search=" xr:uid="{0C75038B-D3F8-471F-83A0-8EF8C2808C08}"/>
+    <hyperlink ref="G49:G50" r:id="rId37" display="https://support.industry.siemens.com/cs/products?search=" xr:uid="{903321B5-20FE-4104-B09A-E138B139072D}"/>
+    <hyperlink ref="G52" r:id="rId38" xr:uid="{0FC34188-903C-4401-830B-83CD3DC5E0EE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="landscape" r:id="rId11"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId39"/>
 </worksheet>
 </file>
 
